--- a/exclusive_system/templates/Шаблон_Анализ_аналогов.xlsx
+++ b/exclusive_system/templates/Шаблон_Анализ_аналогов.xlsx
@@ -38,13 +38,13 @@
       <b val="1"/>
     </font>
     <font>
-      <b val="1"/>
-      <sz val="14"/>
-    </font>
-    <font>
       <i val="1"/>
       <color rgb="00595959"/>
       <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="14"/>
     </font>
     <font>
       <b val="1"/>
@@ -156,8 +156,8 @@
   </cellStyleXfs>
   <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -585,7 +585,7 @@
     <col width="12" customWidth="1" min="22" max="22"/>
     <col width="30" customWidth="1" min="23" max="23"/>
     <col width="13" customWidth="1" min="24" max="24"/>
-    <col width="10" customWidth="1" min="25" max="25"/>
+    <col width="11" customWidth="1" min="25" max="25"/>
     <col width="14" customWidth="1" min="26" max="26"/>
     <col width="8" customWidth="1" min="27" max="27"/>
     <col width="7" customWidth="1" min="28" max="28"/>
@@ -716,7 +716,7 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>Стандартный ремонт</t>
+          <t>С ремонтом (без мебели)</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
@@ -788,6 +788,18 @@
       <c r="L13" s="14" t="n"/>
       <c r="M13" s="14" t="n"/>
       <c r="N13" s="15" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Класс объекта</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>Комфорт</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
@@ -938,7 +950,7 @@
       </c>
       <c r="Y20" s="17" t="inlineStr">
         <is>
-          <t>Общая корректировка, %</t>
+          <t>Общая корректировка без ремонта, %</t>
         </is>
       </c>
       <c r="Z20" s="17" t="inlineStr">
@@ -998,7 +1010,7 @@
         <v/>
       </c>
       <c r="S21" s="23">
-        <f>IF($O21="","",IFERROR(VLOOKUP($B$10,Параметры!$A$10:$C$14,IF($B$7="Аренда",3,2),FALSE)-VLOOKUP(M21,Параметры!$A$10:$C$14,IF($B$7="Аренда",3,2),FALSE),0))</f>
+        <f>IF($O21="","",IFERROR(VLOOKUP($B$10,Параметры!$A$10:$D$12,IF($B$7="Аренда",4,IF($B$14="Премиум",3,2)),FALSE)-VLOOKUP(M21,Параметры!$A$10:$D$12,IF($B$7="Аренда",4,IF($B$14="Премиум",3,2)),FALSE),0))</f>
         <v/>
       </c>
       <c r="T21" s="24" t="n"/>
@@ -1010,7 +1022,7 @@
         <v/>
       </c>
       <c r="Y21" s="21">
-        <f>IF($O21="","",ABS(Q21)+ABS(R21)+ABS(S21/(P21*(1+Q21)))+ABS(N(T21))+ABS(N(U21))+ABS(N(V21)))</f>
+        <f>IF($O21="","",ABS(Q21)+ABS(R21)+ABS(N(T21))+ABS(N(U21))+ABS(N(V21)))</f>
         <v/>
       </c>
       <c r="Z21" s="25">
@@ -1018,7 +1030,7 @@
         <v/>
       </c>
       <c r="AA21" s="25">
-        <f>IF($O21="","",IF(Z21="Да",IFERROR(VLOOKUP(B21,Параметры!$A$17:$B$19,2,FALSE),0.4)/(Y21+0.1),0))</f>
+        <f>IF($O21="","",IF(Z21="Да",IFERROR(VLOOKUP(B21,Параметры!$A$17:$B$19,2,FALSE),0.4)/(Y21+ABS(S21/(P21*(1+Q21)))+0.1),0))</f>
         <v/>
       </c>
       <c r="AB21" s="21">
@@ -1065,7 +1077,7 @@
         <v/>
       </c>
       <c r="S22" s="23">
-        <f>IF($O22="","",IFERROR(VLOOKUP($B$10,Параметры!$A$10:$C$14,IF($B$7="Аренда",3,2),FALSE)-VLOOKUP(M22,Параметры!$A$10:$C$14,IF($B$7="Аренда",3,2),FALSE),0))</f>
+        <f>IF($O22="","",IFERROR(VLOOKUP($B$10,Параметры!$A$10:$D$12,IF($B$7="Аренда",4,IF($B$14="Премиум",3,2)),FALSE)-VLOOKUP(M22,Параметры!$A$10:$D$12,IF($B$7="Аренда",4,IF($B$14="Премиум",3,2)),FALSE),0))</f>
         <v/>
       </c>
       <c r="T22" s="24" t="n"/>
@@ -1077,7 +1089,7 @@
         <v/>
       </c>
       <c r="Y22" s="21">
-        <f>IF($O22="","",ABS(Q22)+ABS(R22)+ABS(S22/(P22*(1+Q22)))+ABS(N(T22))+ABS(N(U22))+ABS(N(V22)))</f>
+        <f>IF($O22="","",ABS(Q22)+ABS(R22)+ABS(N(T22))+ABS(N(U22))+ABS(N(V22)))</f>
         <v/>
       </c>
       <c r="Z22" s="25">
@@ -1085,7 +1097,7 @@
         <v/>
       </c>
       <c r="AA22" s="25">
-        <f>IF($O22="","",IF(Z22="Да",IFERROR(VLOOKUP(B22,Параметры!$A$17:$B$19,2,FALSE),0.4)/(Y22+0.1),0))</f>
+        <f>IF($O22="","",IF(Z22="Да",IFERROR(VLOOKUP(B22,Параметры!$A$17:$B$19,2,FALSE),0.4)/(Y22+ABS(S22/(P22*(1+Q22)))+0.1),0))</f>
         <v/>
       </c>
       <c r="AB22" s="21">
@@ -1132,7 +1144,7 @@
         <v/>
       </c>
       <c r="S23" s="23">
-        <f>IF($O23="","",IFERROR(VLOOKUP($B$10,Параметры!$A$10:$C$14,IF($B$7="Аренда",3,2),FALSE)-VLOOKUP(M23,Параметры!$A$10:$C$14,IF($B$7="Аренда",3,2),FALSE),0))</f>
+        <f>IF($O23="","",IFERROR(VLOOKUP($B$10,Параметры!$A$10:$D$12,IF($B$7="Аренда",4,IF($B$14="Премиум",3,2)),FALSE)-VLOOKUP(M23,Параметры!$A$10:$D$12,IF($B$7="Аренда",4,IF($B$14="Премиум",3,2)),FALSE),0))</f>
         <v/>
       </c>
       <c r="T23" s="24" t="n"/>
@@ -1144,7 +1156,7 @@
         <v/>
       </c>
       <c r="Y23" s="21">
-        <f>IF($O23="","",ABS(Q23)+ABS(R23)+ABS(S23/(P23*(1+Q23)))+ABS(N(T23))+ABS(N(U23))+ABS(N(V23)))</f>
+        <f>IF($O23="","",ABS(Q23)+ABS(R23)+ABS(N(T23))+ABS(N(U23))+ABS(N(V23)))</f>
         <v/>
       </c>
       <c r="Z23" s="25">
@@ -1152,7 +1164,7 @@
         <v/>
       </c>
       <c r="AA23" s="25">
-        <f>IF($O23="","",IF(Z23="Да",IFERROR(VLOOKUP(B23,Параметры!$A$17:$B$19,2,FALSE),0.4)/(Y23+0.1),0))</f>
+        <f>IF($O23="","",IF(Z23="Да",IFERROR(VLOOKUP(B23,Параметры!$A$17:$B$19,2,FALSE),0.4)/(Y23+ABS(S23/(P23*(1+Q23)))+0.1),0))</f>
         <v/>
       </c>
       <c r="AB23" s="21">
@@ -1199,7 +1211,7 @@
         <v/>
       </c>
       <c r="S24" s="23">
-        <f>IF($O24="","",IFERROR(VLOOKUP($B$10,Параметры!$A$10:$C$14,IF($B$7="Аренда",3,2),FALSE)-VLOOKUP(M24,Параметры!$A$10:$C$14,IF($B$7="Аренда",3,2),FALSE),0))</f>
+        <f>IF($O24="","",IFERROR(VLOOKUP($B$10,Параметры!$A$10:$D$12,IF($B$7="Аренда",4,IF($B$14="Премиум",3,2)),FALSE)-VLOOKUP(M24,Параметры!$A$10:$D$12,IF($B$7="Аренда",4,IF($B$14="Премиум",3,2)),FALSE),0))</f>
         <v/>
       </c>
       <c r="T24" s="24" t="n"/>
@@ -1211,7 +1223,7 @@
         <v/>
       </c>
       <c r="Y24" s="21">
-        <f>IF($O24="","",ABS(Q24)+ABS(R24)+ABS(S24/(P24*(1+Q24)))+ABS(N(T24))+ABS(N(U24))+ABS(N(V24)))</f>
+        <f>IF($O24="","",ABS(Q24)+ABS(R24)+ABS(N(T24))+ABS(N(U24))+ABS(N(V24)))</f>
         <v/>
       </c>
       <c r="Z24" s="25">
@@ -1219,7 +1231,7 @@
         <v/>
       </c>
       <c r="AA24" s="25">
-        <f>IF($O24="","",IF(Z24="Да",IFERROR(VLOOKUP(B24,Параметры!$A$17:$B$19,2,FALSE),0.4)/(Y24+0.1),0))</f>
+        <f>IF($O24="","",IF(Z24="Да",IFERROR(VLOOKUP(B24,Параметры!$A$17:$B$19,2,FALSE),0.4)/(Y24+ABS(S24/(P24*(1+Q24)))+0.1),0))</f>
         <v/>
       </c>
       <c r="AB24" s="21">
@@ -1266,7 +1278,7 @@
         <v/>
       </c>
       <c r="S25" s="23">
-        <f>IF($O25="","",IFERROR(VLOOKUP($B$10,Параметры!$A$10:$C$14,IF($B$7="Аренда",3,2),FALSE)-VLOOKUP(M25,Параметры!$A$10:$C$14,IF($B$7="Аренда",3,2),FALSE),0))</f>
+        <f>IF($O25="","",IFERROR(VLOOKUP($B$10,Параметры!$A$10:$D$12,IF($B$7="Аренда",4,IF($B$14="Премиум",3,2)),FALSE)-VLOOKUP(M25,Параметры!$A$10:$D$12,IF($B$7="Аренда",4,IF($B$14="Премиум",3,2)),FALSE),0))</f>
         <v/>
       </c>
       <c r="T25" s="24" t="n"/>
@@ -1278,7 +1290,7 @@
         <v/>
       </c>
       <c r="Y25" s="21">
-        <f>IF($O25="","",ABS(Q25)+ABS(R25)+ABS(S25/(P25*(1+Q25)))+ABS(N(T25))+ABS(N(U25))+ABS(N(V25)))</f>
+        <f>IF($O25="","",ABS(Q25)+ABS(R25)+ABS(N(T25))+ABS(N(U25))+ABS(N(V25)))</f>
         <v/>
       </c>
       <c r="Z25" s="25">
@@ -1286,7 +1298,7 @@
         <v/>
       </c>
       <c r="AA25" s="25">
-        <f>IF($O25="","",IF(Z25="Да",IFERROR(VLOOKUP(B25,Параметры!$A$17:$B$19,2,FALSE),0.4)/(Y25+0.1),0))</f>
+        <f>IF($O25="","",IF(Z25="Да",IFERROR(VLOOKUP(B25,Параметры!$A$17:$B$19,2,FALSE),0.4)/(Y25+ABS(S25/(P25*(1+Q25)))+0.1),0))</f>
         <v/>
       </c>
       <c r="AB25" s="21">
@@ -1333,7 +1345,7 @@
         <v/>
       </c>
       <c r="S26" s="23">
-        <f>IF($O26="","",IFERROR(VLOOKUP($B$10,Параметры!$A$10:$C$14,IF($B$7="Аренда",3,2),FALSE)-VLOOKUP(M26,Параметры!$A$10:$C$14,IF($B$7="Аренда",3,2),FALSE),0))</f>
+        <f>IF($O26="","",IFERROR(VLOOKUP($B$10,Параметры!$A$10:$D$12,IF($B$7="Аренда",4,IF($B$14="Премиум",3,2)),FALSE)-VLOOKUP(M26,Параметры!$A$10:$D$12,IF($B$7="Аренда",4,IF($B$14="Премиум",3,2)),FALSE),0))</f>
         <v/>
       </c>
       <c r="T26" s="24" t="n"/>
@@ -1345,7 +1357,7 @@
         <v/>
       </c>
       <c r="Y26" s="21">
-        <f>IF($O26="","",ABS(Q26)+ABS(R26)+ABS(S26/(P26*(1+Q26)))+ABS(N(T26))+ABS(N(U26))+ABS(N(V26)))</f>
+        <f>IF($O26="","",ABS(Q26)+ABS(R26)+ABS(N(T26))+ABS(N(U26))+ABS(N(V26)))</f>
         <v/>
       </c>
       <c r="Z26" s="25">
@@ -1353,7 +1365,7 @@
         <v/>
       </c>
       <c r="AA26" s="25">
-        <f>IF($O26="","",IF(Z26="Да",IFERROR(VLOOKUP(B26,Параметры!$A$17:$B$19,2,FALSE),0.4)/(Y26+0.1),0))</f>
+        <f>IF($O26="","",IF(Z26="Да",IFERROR(VLOOKUP(B26,Параметры!$A$17:$B$19,2,FALSE),0.4)/(Y26+ABS(S26/(P26*(1+Q26)))+0.1),0))</f>
         <v/>
       </c>
       <c r="AB26" s="21">
@@ -1400,7 +1412,7 @@
         <v/>
       </c>
       <c r="S27" s="23">
-        <f>IF($O27="","",IFERROR(VLOOKUP($B$10,Параметры!$A$10:$C$14,IF($B$7="Аренда",3,2),FALSE)-VLOOKUP(M27,Параметры!$A$10:$C$14,IF($B$7="Аренда",3,2),FALSE),0))</f>
+        <f>IF($O27="","",IFERROR(VLOOKUP($B$10,Параметры!$A$10:$D$12,IF($B$7="Аренда",4,IF($B$14="Премиум",3,2)),FALSE)-VLOOKUP(M27,Параметры!$A$10:$D$12,IF($B$7="Аренда",4,IF($B$14="Премиум",3,2)),FALSE),0))</f>
         <v/>
       </c>
       <c r="T27" s="24" t="n"/>
@@ -1412,7 +1424,7 @@
         <v/>
       </c>
       <c r="Y27" s="21">
-        <f>IF($O27="","",ABS(Q27)+ABS(R27)+ABS(S27/(P27*(1+Q27)))+ABS(N(T27))+ABS(N(U27))+ABS(N(V27)))</f>
+        <f>IF($O27="","",ABS(Q27)+ABS(R27)+ABS(N(T27))+ABS(N(U27))+ABS(N(V27)))</f>
         <v/>
       </c>
       <c r="Z27" s="25">
@@ -1420,7 +1432,7 @@
         <v/>
       </c>
       <c r="AA27" s="25">
-        <f>IF($O27="","",IF(Z27="Да",IFERROR(VLOOKUP(B27,Параметры!$A$17:$B$19,2,FALSE),0.4)/(Y27+0.1),0))</f>
+        <f>IF($O27="","",IF(Z27="Да",IFERROR(VLOOKUP(B27,Параметры!$A$17:$B$19,2,FALSE),0.4)/(Y27+ABS(S27/(P27*(1+Q27)))+0.1),0))</f>
         <v/>
       </c>
       <c r="AB27" s="21">
@@ -1467,7 +1479,7 @@
         <v/>
       </c>
       <c r="S28" s="23">
-        <f>IF($O28="","",IFERROR(VLOOKUP($B$10,Параметры!$A$10:$C$14,IF($B$7="Аренда",3,2),FALSE)-VLOOKUP(M28,Параметры!$A$10:$C$14,IF($B$7="Аренда",3,2),FALSE),0))</f>
+        <f>IF($O28="","",IFERROR(VLOOKUP($B$10,Параметры!$A$10:$D$12,IF($B$7="Аренда",4,IF($B$14="Премиум",3,2)),FALSE)-VLOOKUP(M28,Параметры!$A$10:$D$12,IF($B$7="Аренда",4,IF($B$14="Премиум",3,2)),FALSE),0))</f>
         <v/>
       </c>
       <c r="T28" s="24" t="n"/>
@@ -1479,7 +1491,7 @@
         <v/>
       </c>
       <c r="Y28" s="21">
-        <f>IF($O28="","",ABS(Q28)+ABS(R28)+ABS(S28/(P28*(1+Q28)))+ABS(N(T28))+ABS(N(U28))+ABS(N(V28)))</f>
+        <f>IF($O28="","",ABS(Q28)+ABS(R28)+ABS(N(T28))+ABS(N(U28))+ABS(N(V28)))</f>
         <v/>
       </c>
       <c r="Z28" s="25">
@@ -1487,7 +1499,7 @@
         <v/>
       </c>
       <c r="AA28" s="25">
-        <f>IF($O28="","",IF(Z28="Да",IFERROR(VLOOKUP(B28,Параметры!$A$17:$B$19,2,FALSE),0.4)/(Y28+0.1),0))</f>
+        <f>IF($O28="","",IF(Z28="Да",IFERROR(VLOOKUP(B28,Параметры!$A$17:$B$19,2,FALSE),0.4)/(Y28+ABS(S28/(P28*(1+Q28)))+0.1),0))</f>
         <v/>
       </c>
       <c r="AB28" s="21">
@@ -1534,7 +1546,7 @@
         <v/>
       </c>
       <c r="S29" s="23">
-        <f>IF($O29="","",IFERROR(VLOOKUP($B$10,Параметры!$A$10:$C$14,IF($B$7="Аренда",3,2),FALSE)-VLOOKUP(M29,Параметры!$A$10:$C$14,IF($B$7="Аренда",3,2),FALSE),0))</f>
+        <f>IF($O29="","",IFERROR(VLOOKUP($B$10,Параметры!$A$10:$D$12,IF($B$7="Аренда",4,IF($B$14="Премиум",3,2)),FALSE)-VLOOKUP(M29,Параметры!$A$10:$D$12,IF($B$7="Аренда",4,IF($B$14="Премиум",3,2)),FALSE),0))</f>
         <v/>
       </c>
       <c r="T29" s="24" t="n"/>
@@ -1546,7 +1558,7 @@
         <v/>
       </c>
       <c r="Y29" s="21">
-        <f>IF($O29="","",ABS(Q29)+ABS(R29)+ABS(S29/(P29*(1+Q29)))+ABS(N(T29))+ABS(N(U29))+ABS(N(V29)))</f>
+        <f>IF($O29="","",ABS(Q29)+ABS(R29)+ABS(N(T29))+ABS(N(U29))+ABS(N(V29)))</f>
         <v/>
       </c>
       <c r="Z29" s="25">
@@ -1554,7 +1566,7 @@
         <v/>
       </c>
       <c r="AA29" s="25">
-        <f>IF($O29="","",IF(Z29="Да",IFERROR(VLOOKUP(B29,Параметры!$A$17:$B$19,2,FALSE),0.4)/(Y29+0.1),0))</f>
+        <f>IF($O29="","",IF(Z29="Да",IFERROR(VLOOKUP(B29,Параметры!$A$17:$B$19,2,FALSE),0.4)/(Y29+ABS(S29/(P29*(1+Q29)))+0.1),0))</f>
         <v/>
       </c>
       <c r="AB29" s="21">
@@ -1601,7 +1613,7 @@
         <v/>
       </c>
       <c r="S30" s="23">
-        <f>IF($O30="","",IFERROR(VLOOKUP($B$10,Параметры!$A$10:$C$14,IF($B$7="Аренда",3,2),FALSE)-VLOOKUP(M30,Параметры!$A$10:$C$14,IF($B$7="Аренда",3,2),FALSE),0))</f>
+        <f>IF($O30="","",IFERROR(VLOOKUP($B$10,Параметры!$A$10:$D$12,IF($B$7="Аренда",4,IF($B$14="Премиум",3,2)),FALSE)-VLOOKUP(M30,Параметры!$A$10:$D$12,IF($B$7="Аренда",4,IF($B$14="Премиум",3,2)),FALSE),0))</f>
         <v/>
       </c>
       <c r="T30" s="24" t="n"/>
@@ -1613,7 +1625,7 @@
         <v/>
       </c>
       <c r="Y30" s="21">
-        <f>IF($O30="","",ABS(Q30)+ABS(R30)+ABS(S30/(P30*(1+Q30)))+ABS(N(T30))+ABS(N(U30))+ABS(N(V30)))</f>
+        <f>IF($O30="","",ABS(Q30)+ABS(R30)+ABS(N(T30))+ABS(N(U30))+ABS(N(V30)))</f>
         <v/>
       </c>
       <c r="Z30" s="25">
@@ -1621,7 +1633,7 @@
         <v/>
       </c>
       <c r="AA30" s="25">
-        <f>IF($O30="","",IF(Z30="Да",IFERROR(VLOOKUP(B30,Параметры!$A$17:$B$19,2,FALSE),0.4)/(Y30+0.1),0))</f>
+        <f>IF($O30="","",IF(Z30="Да",IFERROR(VLOOKUP(B30,Параметры!$A$17:$B$19,2,FALSE),0.4)/(Y30+ABS(S30/(P30*(1+Q30)))+0.1),0))</f>
         <v/>
       </c>
       <c r="AB30" s="21">
@@ -1668,7 +1680,7 @@
         <v/>
       </c>
       <c r="S31" s="23">
-        <f>IF($O31="","",IFERROR(VLOOKUP($B$10,Параметры!$A$10:$C$14,IF($B$7="Аренда",3,2),FALSE)-VLOOKUP(M31,Параметры!$A$10:$C$14,IF($B$7="Аренда",3,2),FALSE),0))</f>
+        <f>IF($O31="","",IFERROR(VLOOKUP($B$10,Параметры!$A$10:$D$12,IF($B$7="Аренда",4,IF($B$14="Премиум",3,2)),FALSE)-VLOOKUP(M31,Параметры!$A$10:$D$12,IF($B$7="Аренда",4,IF($B$14="Премиум",3,2)),FALSE),0))</f>
         <v/>
       </c>
       <c r="T31" s="24" t="n"/>
@@ -1680,7 +1692,7 @@
         <v/>
       </c>
       <c r="Y31" s="21">
-        <f>IF($O31="","",ABS(Q31)+ABS(R31)+ABS(S31/(P31*(1+Q31)))+ABS(N(T31))+ABS(N(U31))+ABS(N(V31)))</f>
+        <f>IF($O31="","",ABS(Q31)+ABS(R31)+ABS(N(T31))+ABS(N(U31))+ABS(N(V31)))</f>
         <v/>
       </c>
       <c r="Z31" s="25">
@@ -1688,7 +1700,7 @@
         <v/>
       </c>
       <c r="AA31" s="25">
-        <f>IF($O31="","",IF(Z31="Да",IFERROR(VLOOKUP(B31,Параметры!$A$17:$B$19,2,FALSE),0.4)/(Y31+0.1),0))</f>
+        <f>IF($O31="","",IF(Z31="Да",IFERROR(VLOOKUP(B31,Параметры!$A$17:$B$19,2,FALSE),0.4)/(Y31+ABS(S31/(P31*(1+Q31)))+0.1),0))</f>
         <v/>
       </c>
       <c r="AB31" s="21">
@@ -1735,7 +1747,7 @@
         <v/>
       </c>
       <c r="S32" s="23">
-        <f>IF($O32="","",IFERROR(VLOOKUP($B$10,Параметры!$A$10:$C$14,IF($B$7="Аренда",3,2),FALSE)-VLOOKUP(M32,Параметры!$A$10:$C$14,IF($B$7="Аренда",3,2),FALSE),0))</f>
+        <f>IF($O32="","",IFERROR(VLOOKUP($B$10,Параметры!$A$10:$D$12,IF($B$7="Аренда",4,IF($B$14="Премиум",3,2)),FALSE)-VLOOKUP(M32,Параметры!$A$10:$D$12,IF($B$7="Аренда",4,IF($B$14="Премиум",3,2)),FALSE),0))</f>
         <v/>
       </c>
       <c r="T32" s="24" t="n"/>
@@ -1747,7 +1759,7 @@
         <v/>
       </c>
       <c r="Y32" s="21">
-        <f>IF($O32="","",ABS(Q32)+ABS(R32)+ABS(S32/(P32*(1+Q32)))+ABS(N(T32))+ABS(N(U32))+ABS(N(V32)))</f>
+        <f>IF($O32="","",ABS(Q32)+ABS(R32)+ABS(N(T32))+ABS(N(U32))+ABS(N(V32)))</f>
         <v/>
       </c>
       <c r="Z32" s="25">
@@ -1755,7 +1767,7 @@
         <v/>
       </c>
       <c r="AA32" s="25">
-        <f>IF($O32="","",IF(Z32="Да",IFERROR(VLOOKUP(B32,Параметры!$A$17:$B$19,2,FALSE),0.4)/(Y32+0.1),0))</f>
+        <f>IF($O32="","",IF(Z32="Да",IFERROR(VLOOKUP(B32,Параметры!$A$17:$B$19,2,FALSE),0.4)/(Y32+ABS(S32/(P32*(1+Q32)))+0.1),0))</f>
         <v/>
       </c>
       <c r="AB32" s="21">
@@ -1802,7 +1814,7 @@
         <v/>
       </c>
       <c r="S33" s="23">
-        <f>IF($O33="","",IFERROR(VLOOKUP($B$10,Параметры!$A$10:$C$14,IF($B$7="Аренда",3,2),FALSE)-VLOOKUP(M33,Параметры!$A$10:$C$14,IF($B$7="Аренда",3,2),FALSE),0))</f>
+        <f>IF($O33="","",IFERROR(VLOOKUP($B$10,Параметры!$A$10:$D$12,IF($B$7="Аренда",4,IF($B$14="Премиум",3,2)),FALSE)-VLOOKUP(M33,Параметры!$A$10:$D$12,IF($B$7="Аренда",4,IF($B$14="Премиум",3,2)),FALSE),0))</f>
         <v/>
       </c>
       <c r="T33" s="24" t="n"/>
@@ -1814,7 +1826,7 @@
         <v/>
       </c>
       <c r="Y33" s="21">
-        <f>IF($O33="","",ABS(Q33)+ABS(R33)+ABS(S33/(P33*(1+Q33)))+ABS(N(T33))+ABS(N(U33))+ABS(N(V33)))</f>
+        <f>IF($O33="","",ABS(Q33)+ABS(R33)+ABS(N(T33))+ABS(N(U33))+ABS(N(V33)))</f>
         <v/>
       </c>
       <c r="Z33" s="25">
@@ -1822,7 +1834,7 @@
         <v/>
       </c>
       <c r="AA33" s="25">
-        <f>IF($O33="","",IF(Z33="Да",IFERROR(VLOOKUP(B33,Параметры!$A$17:$B$19,2,FALSE),0.4)/(Y33+0.1),0))</f>
+        <f>IF($O33="","",IF(Z33="Да",IFERROR(VLOOKUP(B33,Параметры!$A$17:$B$19,2,FALSE),0.4)/(Y33+ABS(S33/(P33*(1+Q33)))+0.1),0))</f>
         <v/>
       </c>
       <c r="AB33" s="21">
@@ -1869,7 +1881,7 @@
         <v/>
       </c>
       <c r="S34" s="23">
-        <f>IF($O34="","",IFERROR(VLOOKUP($B$10,Параметры!$A$10:$C$14,IF($B$7="Аренда",3,2),FALSE)-VLOOKUP(M34,Параметры!$A$10:$C$14,IF($B$7="Аренда",3,2),FALSE),0))</f>
+        <f>IF($O34="","",IFERROR(VLOOKUP($B$10,Параметры!$A$10:$D$12,IF($B$7="Аренда",4,IF($B$14="Премиум",3,2)),FALSE)-VLOOKUP(M34,Параметры!$A$10:$D$12,IF($B$7="Аренда",4,IF($B$14="Премиум",3,2)),FALSE),0))</f>
         <v/>
       </c>
       <c r="T34" s="24" t="n"/>
@@ -1881,7 +1893,7 @@
         <v/>
       </c>
       <c r="Y34" s="21">
-        <f>IF($O34="","",ABS(Q34)+ABS(R34)+ABS(S34/(P34*(1+Q34)))+ABS(N(T34))+ABS(N(U34))+ABS(N(V34)))</f>
+        <f>IF($O34="","",ABS(Q34)+ABS(R34)+ABS(N(T34))+ABS(N(U34))+ABS(N(V34)))</f>
         <v/>
       </c>
       <c r="Z34" s="25">
@@ -1889,7 +1901,7 @@
         <v/>
       </c>
       <c r="AA34" s="25">
-        <f>IF($O34="","",IF(Z34="Да",IFERROR(VLOOKUP(B34,Параметры!$A$17:$B$19,2,FALSE),0.4)/(Y34+0.1),0))</f>
+        <f>IF($O34="","",IF(Z34="Да",IFERROR(VLOOKUP(B34,Параметры!$A$17:$B$19,2,FALSE),0.4)/(Y34+ABS(S34/(P34*(1+Q34)))+0.1),0))</f>
         <v/>
       </c>
       <c r="AB34" s="21">
@@ -1936,7 +1948,7 @@
         <v/>
       </c>
       <c r="S35" s="23">
-        <f>IF($O35="","",IFERROR(VLOOKUP($B$10,Параметры!$A$10:$C$14,IF($B$7="Аренда",3,2),FALSE)-VLOOKUP(M35,Параметры!$A$10:$C$14,IF($B$7="Аренда",3,2),FALSE),0))</f>
+        <f>IF($O35="","",IFERROR(VLOOKUP($B$10,Параметры!$A$10:$D$12,IF($B$7="Аренда",4,IF($B$14="Премиум",3,2)),FALSE)-VLOOKUP(M35,Параметры!$A$10:$D$12,IF($B$7="Аренда",4,IF($B$14="Премиум",3,2)),FALSE),0))</f>
         <v/>
       </c>
       <c r="T35" s="24" t="n"/>
@@ -1948,7 +1960,7 @@
         <v/>
       </c>
       <c r="Y35" s="21">
-        <f>IF($O35="","",ABS(Q35)+ABS(R35)+ABS(S35/(P35*(1+Q35)))+ABS(N(T35))+ABS(N(U35))+ABS(N(V35)))</f>
+        <f>IF($O35="","",ABS(Q35)+ABS(R35)+ABS(N(T35))+ABS(N(U35))+ABS(N(V35)))</f>
         <v/>
       </c>
       <c r="Z35" s="25">
@@ -1956,7 +1968,7 @@
         <v/>
       </c>
       <c r="AA35" s="25">
-        <f>IF($O35="","",IF(Z35="Да",IFERROR(VLOOKUP(B35,Параметры!$A$17:$B$19,2,FALSE),0.4)/(Y35+0.1),0))</f>
+        <f>IF($O35="","",IF(Z35="Да",IFERROR(VLOOKUP(B35,Параметры!$A$17:$B$19,2,FALSE),0.4)/(Y35+ABS(S35/(P35*(1+Q35)))+0.1),0))</f>
         <v/>
       </c>
       <c r="AB35" s="21">
@@ -2003,7 +2015,7 @@
         <v/>
       </c>
       <c r="S36" s="23">
-        <f>IF($O36="","",IFERROR(VLOOKUP($B$10,Параметры!$A$10:$C$14,IF($B$7="Аренда",3,2),FALSE)-VLOOKUP(M36,Параметры!$A$10:$C$14,IF($B$7="Аренда",3,2),FALSE),0))</f>
+        <f>IF($O36="","",IFERROR(VLOOKUP($B$10,Параметры!$A$10:$D$12,IF($B$7="Аренда",4,IF($B$14="Премиум",3,2)),FALSE)-VLOOKUP(M36,Параметры!$A$10:$D$12,IF($B$7="Аренда",4,IF($B$14="Премиум",3,2)),FALSE),0))</f>
         <v/>
       </c>
       <c r="T36" s="24" t="n"/>
@@ -2015,7 +2027,7 @@
         <v/>
       </c>
       <c r="Y36" s="21">
-        <f>IF($O36="","",ABS(Q36)+ABS(R36)+ABS(S36/(P36*(1+Q36)))+ABS(N(T36))+ABS(N(U36))+ABS(N(V36)))</f>
+        <f>IF($O36="","",ABS(Q36)+ABS(R36)+ABS(N(T36))+ABS(N(U36))+ABS(N(V36)))</f>
         <v/>
       </c>
       <c r="Z36" s="25">
@@ -2023,7 +2035,7 @@
         <v/>
       </c>
       <c r="AA36" s="25">
-        <f>IF($O36="","",IF(Z36="Да",IFERROR(VLOOKUP(B36,Параметры!$A$17:$B$19,2,FALSE),0.4)/(Y36+0.1),0))</f>
+        <f>IF($O36="","",IF(Z36="Да",IFERROR(VLOOKUP(B36,Параметры!$A$17:$B$19,2,FALSE),0.4)/(Y36+ABS(S36/(P36*(1+Q36)))+0.1),0))</f>
         <v/>
       </c>
       <c r="AB36" s="21">
@@ -2070,7 +2082,7 @@
         <v/>
       </c>
       <c r="S37" s="23">
-        <f>IF($O37="","",IFERROR(VLOOKUP($B$10,Параметры!$A$10:$C$14,IF($B$7="Аренда",3,2),FALSE)-VLOOKUP(M37,Параметры!$A$10:$C$14,IF($B$7="Аренда",3,2),FALSE),0))</f>
+        <f>IF($O37="","",IFERROR(VLOOKUP($B$10,Параметры!$A$10:$D$12,IF($B$7="Аренда",4,IF($B$14="Премиум",3,2)),FALSE)-VLOOKUP(M37,Параметры!$A$10:$D$12,IF($B$7="Аренда",4,IF($B$14="Премиум",3,2)),FALSE),0))</f>
         <v/>
       </c>
       <c r="T37" s="24" t="n"/>
@@ -2082,7 +2094,7 @@
         <v/>
       </c>
       <c r="Y37" s="21">
-        <f>IF($O37="","",ABS(Q37)+ABS(R37)+ABS(S37/(P37*(1+Q37)))+ABS(N(T37))+ABS(N(U37))+ABS(N(V37)))</f>
+        <f>IF($O37="","",ABS(Q37)+ABS(R37)+ABS(N(T37))+ABS(N(U37))+ABS(N(V37)))</f>
         <v/>
       </c>
       <c r="Z37" s="25">
@@ -2090,7 +2102,7 @@
         <v/>
       </c>
       <c r="AA37" s="25">
-        <f>IF($O37="","",IF(Z37="Да",IFERROR(VLOOKUP(B37,Параметры!$A$17:$B$19,2,FALSE),0.4)/(Y37+0.1),0))</f>
+        <f>IF($O37="","",IF(Z37="Да",IFERROR(VLOOKUP(B37,Параметры!$A$17:$B$19,2,FALSE),0.4)/(Y37+ABS(S37/(P37*(1+Q37)))+0.1),0))</f>
         <v/>
       </c>
       <c r="AB37" s="21">
@@ -2137,7 +2149,7 @@
         <v/>
       </c>
       <c r="S38" s="23">
-        <f>IF($O38="","",IFERROR(VLOOKUP($B$10,Параметры!$A$10:$C$14,IF($B$7="Аренда",3,2),FALSE)-VLOOKUP(M38,Параметры!$A$10:$C$14,IF($B$7="Аренда",3,2),FALSE),0))</f>
+        <f>IF($O38="","",IFERROR(VLOOKUP($B$10,Параметры!$A$10:$D$12,IF($B$7="Аренда",4,IF($B$14="Премиум",3,2)),FALSE)-VLOOKUP(M38,Параметры!$A$10:$D$12,IF($B$7="Аренда",4,IF($B$14="Премиум",3,2)),FALSE),0))</f>
         <v/>
       </c>
       <c r="T38" s="24" t="n"/>
@@ -2149,7 +2161,7 @@
         <v/>
       </c>
       <c r="Y38" s="21">
-        <f>IF($O38="","",ABS(Q38)+ABS(R38)+ABS(S38/(P38*(1+Q38)))+ABS(N(T38))+ABS(N(U38))+ABS(N(V38)))</f>
+        <f>IF($O38="","",ABS(Q38)+ABS(R38)+ABS(N(T38))+ABS(N(U38))+ABS(N(V38)))</f>
         <v/>
       </c>
       <c r="Z38" s="25">
@@ -2157,7 +2169,7 @@
         <v/>
       </c>
       <c r="AA38" s="25">
-        <f>IF($O38="","",IF(Z38="Да",IFERROR(VLOOKUP(B38,Параметры!$A$17:$B$19,2,FALSE),0.4)/(Y38+0.1),0))</f>
+        <f>IF($O38="","",IF(Z38="Да",IFERROR(VLOOKUP(B38,Параметры!$A$17:$B$19,2,FALSE),0.4)/(Y38+ABS(S38/(P38*(1+Q38)))+0.1),0))</f>
         <v/>
       </c>
       <c r="AB38" s="21">
@@ -2204,7 +2216,7 @@
         <v/>
       </c>
       <c r="S39" s="23">
-        <f>IF($O39="","",IFERROR(VLOOKUP($B$10,Параметры!$A$10:$C$14,IF($B$7="Аренда",3,2),FALSE)-VLOOKUP(M39,Параметры!$A$10:$C$14,IF($B$7="Аренда",3,2),FALSE),0))</f>
+        <f>IF($O39="","",IFERROR(VLOOKUP($B$10,Параметры!$A$10:$D$12,IF($B$7="Аренда",4,IF($B$14="Премиум",3,2)),FALSE)-VLOOKUP(M39,Параметры!$A$10:$D$12,IF($B$7="Аренда",4,IF($B$14="Премиум",3,2)),FALSE),0))</f>
         <v/>
       </c>
       <c r="T39" s="24" t="n"/>
@@ -2216,7 +2228,7 @@
         <v/>
       </c>
       <c r="Y39" s="21">
-        <f>IF($O39="","",ABS(Q39)+ABS(R39)+ABS(S39/(P39*(1+Q39)))+ABS(N(T39))+ABS(N(U39))+ABS(N(V39)))</f>
+        <f>IF($O39="","",ABS(Q39)+ABS(R39)+ABS(N(T39))+ABS(N(U39))+ABS(N(V39)))</f>
         <v/>
       </c>
       <c r="Z39" s="25">
@@ -2224,7 +2236,7 @@
         <v/>
       </c>
       <c r="AA39" s="25">
-        <f>IF($O39="","",IF(Z39="Да",IFERROR(VLOOKUP(B39,Параметры!$A$17:$B$19,2,FALSE),0.4)/(Y39+0.1),0))</f>
+        <f>IF($O39="","",IF(Z39="Да",IFERROR(VLOOKUP(B39,Параметры!$A$17:$B$19,2,FALSE),0.4)/(Y39+ABS(S39/(P39*(1+Q39)))+0.1),0))</f>
         <v/>
       </c>
       <c r="AB39" s="21">
@@ -2271,7 +2283,7 @@
         <v/>
       </c>
       <c r="S40" s="23">
-        <f>IF($O40="","",IFERROR(VLOOKUP($B$10,Параметры!$A$10:$C$14,IF($B$7="Аренда",3,2),FALSE)-VLOOKUP(M40,Параметры!$A$10:$C$14,IF($B$7="Аренда",3,2),FALSE),0))</f>
+        <f>IF($O40="","",IFERROR(VLOOKUP($B$10,Параметры!$A$10:$D$12,IF($B$7="Аренда",4,IF($B$14="Премиум",3,2)),FALSE)-VLOOKUP(M40,Параметры!$A$10:$D$12,IF($B$7="Аренда",4,IF($B$14="Премиум",3,2)),FALSE),0))</f>
         <v/>
       </c>
       <c r="T40" s="24" t="n"/>
@@ -2283,7 +2295,7 @@
         <v/>
       </c>
       <c r="Y40" s="21">
-        <f>IF($O40="","",ABS(Q40)+ABS(R40)+ABS(S40/(P40*(1+Q40)))+ABS(N(T40))+ABS(N(U40))+ABS(N(V40)))</f>
+        <f>IF($O40="","",ABS(Q40)+ABS(R40)+ABS(N(T40))+ABS(N(U40))+ABS(N(V40)))</f>
         <v/>
       </c>
       <c r="Z40" s="25">
@@ -2291,7 +2303,7 @@
         <v/>
       </c>
       <c r="AA40" s="25">
-        <f>IF($O40="","",IF(Z40="Да",IFERROR(VLOOKUP(B40,Параметры!$A$17:$B$19,2,FALSE),0.4)/(Y40+0.1),0))</f>
+        <f>IF($O40="","",IF(Z40="Да",IFERROR(VLOOKUP(B40,Параметры!$A$17:$B$19,2,FALSE),0.4)/(Y40+ABS(S40/(P40*(1+Q40)))+0.1),0))</f>
         <v/>
       </c>
       <c r="AB40" s="21">
@@ -2338,7 +2350,7 @@
         <v/>
       </c>
       <c r="S41" s="23">
-        <f>IF($O41="","",IFERROR(VLOOKUP($B$10,Параметры!$A$10:$C$14,IF($B$7="Аренда",3,2),FALSE)-VLOOKUP(M41,Параметры!$A$10:$C$14,IF($B$7="Аренда",3,2),FALSE),0))</f>
+        <f>IF($O41="","",IFERROR(VLOOKUP($B$10,Параметры!$A$10:$D$12,IF($B$7="Аренда",4,IF($B$14="Премиум",3,2)),FALSE)-VLOOKUP(M41,Параметры!$A$10:$D$12,IF($B$7="Аренда",4,IF($B$14="Премиум",3,2)),FALSE),0))</f>
         <v/>
       </c>
       <c r="T41" s="24" t="n"/>
@@ -2350,7 +2362,7 @@
         <v/>
       </c>
       <c r="Y41" s="21">
-        <f>IF($O41="","",ABS(Q41)+ABS(R41)+ABS(S41/(P41*(1+Q41)))+ABS(N(T41))+ABS(N(U41))+ABS(N(V41)))</f>
+        <f>IF($O41="","",ABS(Q41)+ABS(R41)+ABS(N(T41))+ABS(N(U41))+ABS(N(V41)))</f>
         <v/>
       </c>
       <c r="Z41" s="25">
@@ -2358,7 +2370,7 @@
         <v/>
       </c>
       <c r="AA41" s="25">
-        <f>IF($O41="","",IF(Z41="Да",IFERROR(VLOOKUP(B41,Параметры!$A$17:$B$19,2,FALSE),0.4)/(Y41+0.1),0))</f>
+        <f>IF($O41="","",IF(Z41="Да",IFERROR(VLOOKUP(B41,Параметры!$A$17:$B$19,2,FALSE),0.4)/(Y41+ABS(S41/(P41*(1+Q41)))+0.1),0))</f>
         <v/>
       </c>
       <c r="AB41" s="21">
@@ -2405,7 +2417,7 @@
         <v/>
       </c>
       <c r="S42" s="23">
-        <f>IF($O42="","",IFERROR(VLOOKUP($B$10,Параметры!$A$10:$C$14,IF($B$7="Аренда",3,2),FALSE)-VLOOKUP(M42,Параметры!$A$10:$C$14,IF($B$7="Аренда",3,2),FALSE),0))</f>
+        <f>IF($O42="","",IFERROR(VLOOKUP($B$10,Параметры!$A$10:$D$12,IF($B$7="Аренда",4,IF($B$14="Премиум",3,2)),FALSE)-VLOOKUP(M42,Параметры!$A$10:$D$12,IF($B$7="Аренда",4,IF($B$14="Премиум",3,2)),FALSE),0))</f>
         <v/>
       </c>
       <c r="T42" s="24" t="n"/>
@@ -2417,7 +2429,7 @@
         <v/>
       </c>
       <c r="Y42" s="21">
-        <f>IF($O42="","",ABS(Q42)+ABS(R42)+ABS(S42/(P42*(1+Q42)))+ABS(N(T42))+ABS(N(U42))+ABS(N(V42)))</f>
+        <f>IF($O42="","",ABS(Q42)+ABS(R42)+ABS(N(T42))+ABS(N(U42))+ABS(N(V42)))</f>
         <v/>
       </c>
       <c r="Z42" s="25">
@@ -2425,7 +2437,7 @@
         <v/>
       </c>
       <c r="AA42" s="25">
-        <f>IF($O42="","",IF(Z42="Да",IFERROR(VLOOKUP(B42,Параметры!$A$17:$B$19,2,FALSE),0.4)/(Y42+0.1),0))</f>
+        <f>IF($O42="","",IF(Z42="Да",IFERROR(VLOOKUP(B42,Параметры!$A$17:$B$19,2,FALSE),0.4)/(Y42+ABS(S42/(P42*(1+Q42)))+0.1),0))</f>
         <v/>
       </c>
       <c r="AB42" s="21">
@@ -2472,7 +2484,7 @@
         <v/>
       </c>
       <c r="S43" s="23">
-        <f>IF($O43="","",IFERROR(VLOOKUP($B$10,Параметры!$A$10:$C$14,IF($B$7="Аренда",3,2),FALSE)-VLOOKUP(M43,Параметры!$A$10:$C$14,IF($B$7="Аренда",3,2),FALSE),0))</f>
+        <f>IF($O43="","",IFERROR(VLOOKUP($B$10,Параметры!$A$10:$D$12,IF($B$7="Аренда",4,IF($B$14="Премиум",3,2)),FALSE)-VLOOKUP(M43,Параметры!$A$10:$D$12,IF($B$7="Аренда",4,IF($B$14="Премиум",3,2)),FALSE),0))</f>
         <v/>
       </c>
       <c r="T43" s="24" t="n"/>
@@ -2484,7 +2496,7 @@
         <v/>
       </c>
       <c r="Y43" s="21">
-        <f>IF($O43="","",ABS(Q43)+ABS(R43)+ABS(S43/(P43*(1+Q43)))+ABS(N(T43))+ABS(N(U43))+ABS(N(V43)))</f>
+        <f>IF($O43="","",ABS(Q43)+ABS(R43)+ABS(N(T43))+ABS(N(U43))+ABS(N(V43)))</f>
         <v/>
       </c>
       <c r="Z43" s="25">
@@ -2492,7 +2504,7 @@
         <v/>
       </c>
       <c r="AA43" s="25">
-        <f>IF($O43="","",IF(Z43="Да",IFERROR(VLOOKUP(B43,Параметры!$A$17:$B$19,2,FALSE),0.4)/(Y43+0.1),0))</f>
+        <f>IF($O43="","",IF(Z43="Да",IFERROR(VLOOKUP(B43,Параметры!$A$17:$B$19,2,FALSE),0.4)/(Y43+ABS(S43/(P43*(1+Q43)))+0.1),0))</f>
         <v/>
       </c>
       <c r="AB43" s="21">
@@ -2539,7 +2551,7 @@
         <v/>
       </c>
       <c r="S44" s="23">
-        <f>IF($O44="","",IFERROR(VLOOKUP($B$10,Параметры!$A$10:$C$14,IF($B$7="Аренда",3,2),FALSE)-VLOOKUP(M44,Параметры!$A$10:$C$14,IF($B$7="Аренда",3,2),FALSE),0))</f>
+        <f>IF($O44="","",IFERROR(VLOOKUP($B$10,Параметры!$A$10:$D$12,IF($B$7="Аренда",4,IF($B$14="Премиум",3,2)),FALSE)-VLOOKUP(M44,Параметры!$A$10:$D$12,IF($B$7="Аренда",4,IF($B$14="Премиум",3,2)),FALSE),0))</f>
         <v/>
       </c>
       <c r="T44" s="24" t="n"/>
@@ -2551,7 +2563,7 @@
         <v/>
       </c>
       <c r="Y44" s="21">
-        <f>IF($O44="","",ABS(Q44)+ABS(R44)+ABS(S44/(P44*(1+Q44)))+ABS(N(T44))+ABS(N(U44))+ABS(N(V44)))</f>
+        <f>IF($O44="","",ABS(Q44)+ABS(R44)+ABS(N(T44))+ABS(N(U44))+ABS(N(V44)))</f>
         <v/>
       </c>
       <c r="Z44" s="25">
@@ -2559,7 +2571,7 @@
         <v/>
       </c>
       <c r="AA44" s="25">
-        <f>IF($O44="","",IF(Z44="Да",IFERROR(VLOOKUP(B44,Параметры!$A$17:$B$19,2,FALSE),0.4)/(Y44+0.1),0))</f>
+        <f>IF($O44="","",IF(Z44="Да",IFERROR(VLOOKUP(B44,Параметры!$A$17:$B$19,2,FALSE),0.4)/(Y44+ABS(S44/(P44*(1+Q44)))+0.1),0))</f>
         <v/>
       </c>
       <c r="AB44" s="21">
@@ -2606,7 +2618,7 @@
         <v/>
       </c>
       <c r="S45" s="23">
-        <f>IF($O45="","",IFERROR(VLOOKUP($B$10,Параметры!$A$10:$C$14,IF($B$7="Аренда",3,2),FALSE)-VLOOKUP(M45,Параметры!$A$10:$C$14,IF($B$7="Аренда",3,2),FALSE),0))</f>
+        <f>IF($O45="","",IFERROR(VLOOKUP($B$10,Параметры!$A$10:$D$12,IF($B$7="Аренда",4,IF($B$14="Премиум",3,2)),FALSE)-VLOOKUP(M45,Параметры!$A$10:$D$12,IF($B$7="Аренда",4,IF($B$14="Премиум",3,2)),FALSE),0))</f>
         <v/>
       </c>
       <c r="T45" s="24" t="n"/>
@@ -2618,7 +2630,7 @@
         <v/>
       </c>
       <c r="Y45" s="21">
-        <f>IF($O45="","",ABS(Q45)+ABS(R45)+ABS(S45/(P45*(1+Q45)))+ABS(N(T45))+ABS(N(U45))+ABS(N(V45)))</f>
+        <f>IF($O45="","",ABS(Q45)+ABS(R45)+ABS(N(T45))+ABS(N(U45))+ABS(N(V45)))</f>
         <v/>
       </c>
       <c r="Z45" s="25">
@@ -2626,7 +2638,7 @@
         <v/>
       </c>
       <c r="AA45" s="25">
-        <f>IF($O45="","",IF(Z45="Да",IFERROR(VLOOKUP(B45,Параметры!$A$17:$B$19,2,FALSE),0.4)/(Y45+0.1),0))</f>
+        <f>IF($O45="","",IF(Z45="Да",IFERROR(VLOOKUP(B45,Параметры!$A$17:$B$19,2,FALSE),0.4)/(Y45+ABS(S45/(P45*(1+Q45)))+0.1),0))</f>
         <v/>
       </c>
       <c r="AB45" s="21">
@@ -2673,7 +2685,7 @@
         <v/>
       </c>
       <c r="S46" s="23">
-        <f>IF($O46="","",IFERROR(VLOOKUP($B$10,Параметры!$A$10:$C$14,IF($B$7="Аренда",3,2),FALSE)-VLOOKUP(M46,Параметры!$A$10:$C$14,IF($B$7="Аренда",3,2),FALSE),0))</f>
+        <f>IF($O46="","",IFERROR(VLOOKUP($B$10,Параметры!$A$10:$D$12,IF($B$7="Аренда",4,IF($B$14="Премиум",3,2)),FALSE)-VLOOKUP(M46,Параметры!$A$10:$D$12,IF($B$7="Аренда",4,IF($B$14="Премиум",3,2)),FALSE),0))</f>
         <v/>
       </c>
       <c r="T46" s="24" t="n"/>
@@ -2685,7 +2697,7 @@
         <v/>
       </c>
       <c r="Y46" s="21">
-        <f>IF($O46="","",ABS(Q46)+ABS(R46)+ABS(S46/(P46*(1+Q46)))+ABS(N(T46))+ABS(N(U46))+ABS(N(V46)))</f>
+        <f>IF($O46="","",ABS(Q46)+ABS(R46)+ABS(N(T46))+ABS(N(U46))+ABS(N(V46)))</f>
         <v/>
       </c>
       <c r="Z46" s="25">
@@ -2693,7 +2705,7 @@
         <v/>
       </c>
       <c r="AA46" s="25">
-        <f>IF($O46="","",IF(Z46="Да",IFERROR(VLOOKUP(B46,Параметры!$A$17:$B$19,2,FALSE),0.4)/(Y46+0.1),0))</f>
+        <f>IF($O46="","",IF(Z46="Да",IFERROR(VLOOKUP(B46,Параметры!$A$17:$B$19,2,FALSE),0.4)/(Y46+ABS(S46/(P46*(1+Q46)))+0.1),0))</f>
         <v/>
       </c>
       <c r="AB46" s="21">
@@ -2740,7 +2752,7 @@
         <v/>
       </c>
       <c r="S47" s="23">
-        <f>IF($O47="","",IFERROR(VLOOKUP($B$10,Параметры!$A$10:$C$14,IF($B$7="Аренда",3,2),FALSE)-VLOOKUP(M47,Параметры!$A$10:$C$14,IF($B$7="Аренда",3,2),FALSE),0))</f>
+        <f>IF($O47="","",IFERROR(VLOOKUP($B$10,Параметры!$A$10:$D$12,IF($B$7="Аренда",4,IF($B$14="Премиум",3,2)),FALSE)-VLOOKUP(M47,Параметры!$A$10:$D$12,IF($B$7="Аренда",4,IF($B$14="Премиум",3,2)),FALSE),0))</f>
         <v/>
       </c>
       <c r="T47" s="24" t="n"/>
@@ -2752,7 +2764,7 @@
         <v/>
       </c>
       <c r="Y47" s="21">
-        <f>IF($O47="","",ABS(Q47)+ABS(R47)+ABS(S47/(P47*(1+Q47)))+ABS(N(T47))+ABS(N(U47))+ABS(N(V47)))</f>
+        <f>IF($O47="","",ABS(Q47)+ABS(R47)+ABS(N(T47))+ABS(N(U47))+ABS(N(V47)))</f>
         <v/>
       </c>
       <c r="Z47" s="25">
@@ -2760,7 +2772,7 @@
         <v/>
       </c>
       <c r="AA47" s="25">
-        <f>IF($O47="","",IF(Z47="Да",IFERROR(VLOOKUP(B47,Параметры!$A$17:$B$19,2,FALSE),0.4)/(Y47+0.1),0))</f>
+        <f>IF($O47="","",IF(Z47="Да",IFERROR(VLOOKUP(B47,Параметры!$A$17:$B$19,2,FALSE),0.4)/(Y47+ABS(S47/(P47*(1+Q47)))+0.1),0))</f>
         <v/>
       </c>
       <c r="AB47" s="21">
@@ -2807,7 +2819,7 @@
         <v/>
       </c>
       <c r="S48" s="23">
-        <f>IF($O48="","",IFERROR(VLOOKUP($B$10,Параметры!$A$10:$C$14,IF($B$7="Аренда",3,2),FALSE)-VLOOKUP(M48,Параметры!$A$10:$C$14,IF($B$7="Аренда",3,2),FALSE),0))</f>
+        <f>IF($O48="","",IFERROR(VLOOKUP($B$10,Параметры!$A$10:$D$12,IF($B$7="Аренда",4,IF($B$14="Премиум",3,2)),FALSE)-VLOOKUP(M48,Параметры!$A$10:$D$12,IF($B$7="Аренда",4,IF($B$14="Премиум",3,2)),FALSE),0))</f>
         <v/>
       </c>
       <c r="T48" s="24" t="n"/>
@@ -2819,7 +2831,7 @@
         <v/>
       </c>
       <c r="Y48" s="21">
-        <f>IF($O48="","",ABS(Q48)+ABS(R48)+ABS(S48/(P48*(1+Q48)))+ABS(N(T48))+ABS(N(U48))+ABS(N(V48)))</f>
+        <f>IF($O48="","",ABS(Q48)+ABS(R48)+ABS(N(T48))+ABS(N(U48))+ABS(N(V48)))</f>
         <v/>
       </c>
       <c r="Z48" s="25">
@@ -2827,7 +2839,7 @@
         <v/>
       </c>
       <c r="AA48" s="25">
-        <f>IF($O48="","",IF(Z48="Да",IFERROR(VLOOKUP(B48,Параметры!$A$17:$B$19,2,FALSE),0.4)/(Y48+0.1),0))</f>
+        <f>IF($O48="","",IF(Z48="Да",IFERROR(VLOOKUP(B48,Параметры!$A$17:$B$19,2,FALSE),0.4)/(Y48+ABS(S48/(P48*(1+Q48)))+0.1),0))</f>
         <v/>
       </c>
       <c r="AB48" s="21">
@@ -2874,7 +2886,7 @@
         <v/>
       </c>
       <c r="S49" s="23">
-        <f>IF($O49="","",IFERROR(VLOOKUP($B$10,Параметры!$A$10:$C$14,IF($B$7="Аренда",3,2),FALSE)-VLOOKUP(M49,Параметры!$A$10:$C$14,IF($B$7="Аренда",3,2),FALSE),0))</f>
+        <f>IF($O49="","",IFERROR(VLOOKUP($B$10,Параметры!$A$10:$D$12,IF($B$7="Аренда",4,IF($B$14="Премиум",3,2)),FALSE)-VLOOKUP(M49,Параметры!$A$10:$D$12,IF($B$7="Аренда",4,IF($B$14="Премиум",3,2)),FALSE),0))</f>
         <v/>
       </c>
       <c r="T49" s="24" t="n"/>
@@ -2886,7 +2898,7 @@
         <v/>
       </c>
       <c r="Y49" s="21">
-        <f>IF($O49="","",ABS(Q49)+ABS(R49)+ABS(S49/(P49*(1+Q49)))+ABS(N(T49))+ABS(N(U49))+ABS(N(V49)))</f>
+        <f>IF($O49="","",ABS(Q49)+ABS(R49)+ABS(N(T49))+ABS(N(U49))+ABS(N(V49)))</f>
         <v/>
       </c>
       <c r="Z49" s="25">
@@ -2894,7 +2906,7 @@
         <v/>
       </c>
       <c r="AA49" s="25">
-        <f>IF($O49="","",IF(Z49="Да",IFERROR(VLOOKUP(B49,Параметры!$A$17:$B$19,2,FALSE),0.4)/(Y49+0.1),0))</f>
+        <f>IF($O49="","",IF(Z49="Да",IFERROR(VLOOKUP(B49,Параметры!$A$17:$B$19,2,FALSE),0.4)/(Y49+ABS(S49/(P49*(1+Q49)))+0.1),0))</f>
         <v/>
       </c>
       <c r="AB49" s="21">
@@ -2941,7 +2953,7 @@
         <v/>
       </c>
       <c r="S50" s="23">
-        <f>IF($O50="","",IFERROR(VLOOKUP($B$10,Параметры!$A$10:$C$14,IF($B$7="Аренда",3,2),FALSE)-VLOOKUP(M50,Параметры!$A$10:$C$14,IF($B$7="Аренда",3,2),FALSE),0))</f>
+        <f>IF($O50="","",IFERROR(VLOOKUP($B$10,Параметры!$A$10:$D$12,IF($B$7="Аренда",4,IF($B$14="Премиум",3,2)),FALSE)-VLOOKUP(M50,Параметры!$A$10:$D$12,IF($B$7="Аренда",4,IF($B$14="Премиум",3,2)),FALSE),0))</f>
         <v/>
       </c>
       <c r="T50" s="24" t="n"/>
@@ -2953,7 +2965,7 @@
         <v/>
       </c>
       <c r="Y50" s="21">
-        <f>IF($O50="","",ABS(Q50)+ABS(R50)+ABS(S50/(P50*(1+Q50)))+ABS(N(T50))+ABS(N(U50))+ABS(N(V50)))</f>
+        <f>IF($O50="","",ABS(Q50)+ABS(R50)+ABS(N(T50))+ABS(N(U50))+ABS(N(V50)))</f>
         <v/>
       </c>
       <c r="Z50" s="25">
@@ -2961,7 +2973,7 @@
         <v/>
       </c>
       <c r="AA50" s="25">
-        <f>IF($O50="","",IF(Z50="Да",IFERROR(VLOOKUP(B50,Параметры!$A$17:$B$19,2,FALSE),0.4)/(Y50+0.1),0))</f>
+        <f>IF($O50="","",IF(Z50="Да",IFERROR(VLOOKUP(B50,Параметры!$A$17:$B$19,2,FALSE),0.4)/(Y50+ABS(S50/(P50*(1+Q50)))+0.1),0))</f>
         <v/>
       </c>
       <c r="AB50" s="21">
@@ -3008,7 +3020,7 @@
         <v/>
       </c>
       <c r="S51" s="23">
-        <f>IF($O51="","",IFERROR(VLOOKUP($B$10,Параметры!$A$10:$C$14,IF($B$7="Аренда",3,2),FALSE)-VLOOKUP(M51,Параметры!$A$10:$C$14,IF($B$7="Аренда",3,2),FALSE),0))</f>
+        <f>IF($O51="","",IFERROR(VLOOKUP($B$10,Параметры!$A$10:$D$12,IF($B$7="Аренда",4,IF($B$14="Премиум",3,2)),FALSE)-VLOOKUP(M51,Параметры!$A$10:$D$12,IF($B$7="Аренда",4,IF($B$14="Премиум",3,2)),FALSE),0))</f>
         <v/>
       </c>
       <c r="T51" s="24" t="n"/>
@@ -3020,7 +3032,7 @@
         <v/>
       </c>
       <c r="Y51" s="21">
-        <f>IF($O51="","",ABS(Q51)+ABS(R51)+ABS(S51/(P51*(1+Q51)))+ABS(N(T51))+ABS(N(U51))+ABS(N(V51)))</f>
+        <f>IF($O51="","",ABS(Q51)+ABS(R51)+ABS(N(T51))+ABS(N(U51))+ABS(N(V51)))</f>
         <v/>
       </c>
       <c r="Z51" s="25">
@@ -3028,7 +3040,7 @@
         <v/>
       </c>
       <c r="AA51" s="25">
-        <f>IF($O51="","",IF(Z51="Да",IFERROR(VLOOKUP(B51,Параметры!$A$17:$B$19,2,FALSE),0.4)/(Y51+0.1),0))</f>
+        <f>IF($O51="","",IF(Z51="Да",IFERROR(VLOOKUP(B51,Параметры!$A$17:$B$19,2,FALSE),0.4)/(Y51+ABS(S51/(P51*(1+Q51)))+0.1),0))</f>
         <v/>
       </c>
       <c r="AB51" s="21">
@@ -3075,7 +3087,7 @@
         <v/>
       </c>
       <c r="S52" s="23">
-        <f>IF($O52="","",IFERROR(VLOOKUP($B$10,Параметры!$A$10:$C$14,IF($B$7="Аренда",3,2),FALSE)-VLOOKUP(M52,Параметры!$A$10:$C$14,IF($B$7="Аренда",3,2),FALSE),0))</f>
+        <f>IF($O52="","",IFERROR(VLOOKUP($B$10,Параметры!$A$10:$D$12,IF($B$7="Аренда",4,IF($B$14="Премиум",3,2)),FALSE)-VLOOKUP(M52,Параметры!$A$10:$D$12,IF($B$7="Аренда",4,IF($B$14="Премиум",3,2)),FALSE),0))</f>
         <v/>
       </c>
       <c r="T52" s="24" t="n"/>
@@ -3087,7 +3099,7 @@
         <v/>
       </c>
       <c r="Y52" s="21">
-        <f>IF($O52="","",ABS(Q52)+ABS(R52)+ABS(S52/(P52*(1+Q52)))+ABS(N(T52))+ABS(N(U52))+ABS(N(V52)))</f>
+        <f>IF($O52="","",ABS(Q52)+ABS(R52)+ABS(N(T52))+ABS(N(U52))+ABS(N(V52)))</f>
         <v/>
       </c>
       <c r="Z52" s="25">
@@ -3095,7 +3107,7 @@
         <v/>
       </c>
       <c r="AA52" s="25">
-        <f>IF($O52="","",IF(Z52="Да",IFERROR(VLOOKUP(B52,Параметры!$A$17:$B$19,2,FALSE),0.4)/(Y52+0.1),0))</f>
+        <f>IF($O52="","",IF(Z52="Да",IFERROR(VLOOKUP(B52,Параметры!$A$17:$B$19,2,FALSE),0.4)/(Y52+ABS(S52/(P52*(1+Q52)))+0.1),0))</f>
         <v/>
       </c>
       <c r="AB52" s="21">
@@ -3142,7 +3154,7 @@
         <v/>
       </c>
       <c r="S53" s="23">
-        <f>IF($O53="","",IFERROR(VLOOKUP($B$10,Параметры!$A$10:$C$14,IF($B$7="Аренда",3,2),FALSE)-VLOOKUP(M53,Параметры!$A$10:$C$14,IF($B$7="Аренда",3,2),FALSE),0))</f>
+        <f>IF($O53="","",IFERROR(VLOOKUP($B$10,Параметры!$A$10:$D$12,IF($B$7="Аренда",4,IF($B$14="Премиум",3,2)),FALSE)-VLOOKUP(M53,Параметры!$A$10:$D$12,IF($B$7="Аренда",4,IF($B$14="Премиум",3,2)),FALSE),0))</f>
         <v/>
       </c>
       <c r="T53" s="24" t="n"/>
@@ -3154,7 +3166,7 @@
         <v/>
       </c>
       <c r="Y53" s="21">
-        <f>IF($O53="","",ABS(Q53)+ABS(R53)+ABS(S53/(P53*(1+Q53)))+ABS(N(T53))+ABS(N(U53))+ABS(N(V53)))</f>
+        <f>IF($O53="","",ABS(Q53)+ABS(R53)+ABS(N(T53))+ABS(N(U53))+ABS(N(V53)))</f>
         <v/>
       </c>
       <c r="Z53" s="25">
@@ -3162,7 +3174,7 @@
         <v/>
       </c>
       <c r="AA53" s="25">
-        <f>IF($O53="","",IF(Z53="Да",IFERROR(VLOOKUP(B53,Параметры!$A$17:$B$19,2,FALSE),0.4)/(Y53+0.1),0))</f>
+        <f>IF($O53="","",IF(Z53="Да",IFERROR(VLOOKUP(B53,Параметры!$A$17:$B$19,2,FALSE),0.4)/(Y53+ABS(S53/(P53*(1+Q53)))+0.1),0))</f>
         <v/>
       </c>
       <c r="AB53" s="21">
@@ -3209,7 +3221,7 @@
         <v/>
       </c>
       <c r="S54" s="23">
-        <f>IF($O54="","",IFERROR(VLOOKUP($B$10,Параметры!$A$10:$C$14,IF($B$7="Аренда",3,2),FALSE)-VLOOKUP(M54,Параметры!$A$10:$C$14,IF($B$7="Аренда",3,2),FALSE),0))</f>
+        <f>IF($O54="","",IFERROR(VLOOKUP($B$10,Параметры!$A$10:$D$12,IF($B$7="Аренда",4,IF($B$14="Премиум",3,2)),FALSE)-VLOOKUP(M54,Параметры!$A$10:$D$12,IF($B$7="Аренда",4,IF($B$14="Премиум",3,2)),FALSE),0))</f>
         <v/>
       </c>
       <c r="T54" s="24" t="n"/>
@@ -3221,7 +3233,7 @@
         <v/>
       </c>
       <c r="Y54" s="21">
-        <f>IF($O54="","",ABS(Q54)+ABS(R54)+ABS(S54/(P54*(1+Q54)))+ABS(N(T54))+ABS(N(U54))+ABS(N(V54)))</f>
+        <f>IF($O54="","",ABS(Q54)+ABS(R54)+ABS(N(T54))+ABS(N(U54))+ABS(N(V54)))</f>
         <v/>
       </c>
       <c r="Z54" s="25">
@@ -3229,7 +3241,7 @@
         <v/>
       </c>
       <c r="AA54" s="25">
-        <f>IF($O54="","",IF(Z54="Да",IFERROR(VLOOKUP(B54,Параметры!$A$17:$B$19,2,FALSE),0.4)/(Y54+0.1),0))</f>
+        <f>IF($O54="","",IF(Z54="Да",IFERROR(VLOOKUP(B54,Параметры!$A$17:$B$19,2,FALSE),0.4)/(Y54+ABS(S54/(P54*(1+Q54)))+0.1),0))</f>
         <v/>
       </c>
       <c r="AB54" s="21">
@@ -3276,7 +3288,7 @@
         <v/>
       </c>
       <c r="S55" s="23">
-        <f>IF($O55="","",IFERROR(VLOOKUP($B$10,Параметры!$A$10:$C$14,IF($B$7="Аренда",3,2),FALSE)-VLOOKUP(M55,Параметры!$A$10:$C$14,IF($B$7="Аренда",3,2),FALSE),0))</f>
+        <f>IF($O55="","",IFERROR(VLOOKUP($B$10,Параметры!$A$10:$D$12,IF($B$7="Аренда",4,IF($B$14="Премиум",3,2)),FALSE)-VLOOKUP(M55,Параметры!$A$10:$D$12,IF($B$7="Аренда",4,IF($B$14="Премиум",3,2)),FALSE),0))</f>
         <v/>
       </c>
       <c r="T55" s="24" t="n"/>
@@ -3288,7 +3300,7 @@
         <v/>
       </c>
       <c r="Y55" s="21">
-        <f>IF($O55="","",ABS(Q55)+ABS(R55)+ABS(S55/(P55*(1+Q55)))+ABS(N(T55))+ABS(N(U55))+ABS(N(V55)))</f>
+        <f>IF($O55="","",ABS(Q55)+ABS(R55)+ABS(N(T55))+ABS(N(U55))+ABS(N(V55)))</f>
         <v/>
       </c>
       <c r="Z55" s="25">
@@ -3296,7 +3308,7 @@
         <v/>
       </c>
       <c r="AA55" s="25">
-        <f>IF($O55="","",IF(Z55="Да",IFERROR(VLOOKUP(B55,Параметры!$A$17:$B$19,2,FALSE),0.4)/(Y55+0.1),0))</f>
+        <f>IF($O55="","",IF(Z55="Да",IFERROR(VLOOKUP(B55,Параметры!$A$17:$B$19,2,FALSE),0.4)/(Y55+ABS(S55/(P55*(1+Q55)))+0.1),0))</f>
         <v/>
       </c>
       <c r="AB55" s="21">
@@ -3343,7 +3355,7 @@
         <v/>
       </c>
       <c r="S56" s="23">
-        <f>IF($O56="","",IFERROR(VLOOKUP($B$10,Параметры!$A$10:$C$14,IF($B$7="Аренда",3,2),FALSE)-VLOOKUP(M56,Параметры!$A$10:$C$14,IF($B$7="Аренда",3,2),FALSE),0))</f>
+        <f>IF($O56="","",IFERROR(VLOOKUP($B$10,Параметры!$A$10:$D$12,IF($B$7="Аренда",4,IF($B$14="Премиум",3,2)),FALSE)-VLOOKUP(M56,Параметры!$A$10:$D$12,IF($B$7="Аренда",4,IF($B$14="Премиум",3,2)),FALSE),0))</f>
         <v/>
       </c>
       <c r="T56" s="24" t="n"/>
@@ -3355,7 +3367,7 @@
         <v/>
       </c>
       <c r="Y56" s="21">
-        <f>IF($O56="","",ABS(Q56)+ABS(R56)+ABS(S56/(P56*(1+Q56)))+ABS(N(T56))+ABS(N(U56))+ABS(N(V56)))</f>
+        <f>IF($O56="","",ABS(Q56)+ABS(R56)+ABS(N(T56))+ABS(N(U56))+ABS(N(V56)))</f>
         <v/>
       </c>
       <c r="Z56" s="25">
@@ -3363,7 +3375,7 @@
         <v/>
       </c>
       <c r="AA56" s="25">
-        <f>IF($O56="","",IF(Z56="Да",IFERROR(VLOOKUP(B56,Параметры!$A$17:$B$19,2,FALSE),0.4)/(Y56+0.1),0))</f>
+        <f>IF($O56="","",IF(Z56="Да",IFERROR(VLOOKUP(B56,Параметры!$A$17:$B$19,2,FALSE),0.4)/(Y56+ABS(S56/(P56*(1+Q56)))+0.1),0))</f>
         <v/>
       </c>
       <c r="AB56" s="21">
@@ -3410,7 +3422,7 @@
         <v/>
       </c>
       <c r="S57" s="23">
-        <f>IF($O57="","",IFERROR(VLOOKUP($B$10,Параметры!$A$10:$C$14,IF($B$7="Аренда",3,2),FALSE)-VLOOKUP(M57,Параметры!$A$10:$C$14,IF($B$7="Аренда",3,2),FALSE),0))</f>
+        <f>IF($O57="","",IFERROR(VLOOKUP($B$10,Параметры!$A$10:$D$12,IF($B$7="Аренда",4,IF($B$14="Премиум",3,2)),FALSE)-VLOOKUP(M57,Параметры!$A$10:$D$12,IF($B$7="Аренда",4,IF($B$14="Премиум",3,2)),FALSE),0))</f>
         <v/>
       </c>
       <c r="T57" s="24" t="n"/>
@@ -3422,7 +3434,7 @@
         <v/>
       </c>
       <c r="Y57" s="21">
-        <f>IF($O57="","",ABS(Q57)+ABS(R57)+ABS(S57/(P57*(1+Q57)))+ABS(N(T57))+ABS(N(U57))+ABS(N(V57)))</f>
+        <f>IF($O57="","",ABS(Q57)+ABS(R57)+ABS(N(T57))+ABS(N(U57))+ABS(N(V57)))</f>
         <v/>
       </c>
       <c r="Z57" s="25">
@@ -3430,7 +3442,7 @@
         <v/>
       </c>
       <c r="AA57" s="25">
-        <f>IF($O57="","",IF(Z57="Да",IFERROR(VLOOKUP(B57,Параметры!$A$17:$B$19,2,FALSE),0.4)/(Y57+0.1),0))</f>
+        <f>IF($O57="","",IF(Z57="Да",IFERROR(VLOOKUP(B57,Параметры!$A$17:$B$19,2,FALSE),0.4)/(Y57+ABS(S57/(P57*(1+Q57)))+0.1),0))</f>
         <v/>
       </c>
       <c r="AB57" s="21">
@@ -3477,7 +3489,7 @@
         <v/>
       </c>
       <c r="S58" s="23">
-        <f>IF($O58="","",IFERROR(VLOOKUP($B$10,Параметры!$A$10:$C$14,IF($B$7="Аренда",3,2),FALSE)-VLOOKUP(M58,Параметры!$A$10:$C$14,IF($B$7="Аренда",3,2),FALSE),0))</f>
+        <f>IF($O58="","",IFERROR(VLOOKUP($B$10,Параметры!$A$10:$D$12,IF($B$7="Аренда",4,IF($B$14="Премиум",3,2)),FALSE)-VLOOKUP(M58,Параметры!$A$10:$D$12,IF($B$7="Аренда",4,IF($B$14="Премиум",3,2)),FALSE),0))</f>
         <v/>
       </c>
       <c r="T58" s="24" t="n"/>
@@ -3489,7 +3501,7 @@
         <v/>
       </c>
       <c r="Y58" s="21">
-        <f>IF($O58="","",ABS(Q58)+ABS(R58)+ABS(S58/(P58*(1+Q58)))+ABS(N(T58))+ABS(N(U58))+ABS(N(V58)))</f>
+        <f>IF($O58="","",ABS(Q58)+ABS(R58)+ABS(N(T58))+ABS(N(U58))+ABS(N(V58)))</f>
         <v/>
       </c>
       <c r="Z58" s="25">
@@ -3497,7 +3509,7 @@
         <v/>
       </c>
       <c r="AA58" s="25">
-        <f>IF($O58="","",IF(Z58="Да",IFERROR(VLOOKUP(B58,Параметры!$A$17:$B$19,2,FALSE),0.4)/(Y58+0.1),0))</f>
+        <f>IF($O58="","",IF(Z58="Да",IFERROR(VLOOKUP(B58,Параметры!$A$17:$B$19,2,FALSE),0.4)/(Y58+ABS(S58/(P58*(1+Q58)))+0.1),0))</f>
         <v/>
       </c>
       <c r="AB58" s="21">
@@ -3544,7 +3556,7 @@
         <v/>
       </c>
       <c r="S59" s="23">
-        <f>IF($O59="","",IFERROR(VLOOKUP($B$10,Параметры!$A$10:$C$14,IF($B$7="Аренда",3,2),FALSE)-VLOOKUP(M59,Параметры!$A$10:$C$14,IF($B$7="Аренда",3,2),FALSE),0))</f>
+        <f>IF($O59="","",IFERROR(VLOOKUP($B$10,Параметры!$A$10:$D$12,IF($B$7="Аренда",4,IF($B$14="Премиум",3,2)),FALSE)-VLOOKUP(M59,Параметры!$A$10:$D$12,IF($B$7="Аренда",4,IF($B$14="Премиум",3,2)),FALSE),0))</f>
         <v/>
       </c>
       <c r="T59" s="24" t="n"/>
@@ -3556,7 +3568,7 @@
         <v/>
       </c>
       <c r="Y59" s="21">
-        <f>IF($O59="","",ABS(Q59)+ABS(R59)+ABS(S59/(P59*(1+Q59)))+ABS(N(T59))+ABS(N(U59))+ABS(N(V59)))</f>
+        <f>IF($O59="","",ABS(Q59)+ABS(R59)+ABS(N(T59))+ABS(N(U59))+ABS(N(V59)))</f>
         <v/>
       </c>
       <c r="Z59" s="25">
@@ -3564,7 +3576,7 @@
         <v/>
       </c>
       <c r="AA59" s="25">
-        <f>IF($O59="","",IF(Z59="Да",IFERROR(VLOOKUP(B59,Параметры!$A$17:$B$19,2,FALSE),0.4)/(Y59+0.1),0))</f>
+        <f>IF($O59="","",IF(Z59="Да",IFERROR(VLOOKUP(B59,Параметры!$A$17:$B$19,2,FALSE),0.4)/(Y59+ABS(S59/(P59*(1+Q59)))+0.1),0))</f>
         <v/>
       </c>
       <c r="AB59" s="21">
@@ -3611,7 +3623,7 @@
         <v/>
       </c>
       <c r="S60" s="23">
-        <f>IF($O60="","",IFERROR(VLOOKUP($B$10,Параметры!$A$10:$C$14,IF($B$7="Аренда",3,2),FALSE)-VLOOKUP(M60,Параметры!$A$10:$C$14,IF($B$7="Аренда",3,2),FALSE),0))</f>
+        <f>IF($O60="","",IFERROR(VLOOKUP($B$10,Параметры!$A$10:$D$12,IF($B$7="Аренда",4,IF($B$14="Премиум",3,2)),FALSE)-VLOOKUP(M60,Параметры!$A$10:$D$12,IF($B$7="Аренда",4,IF($B$14="Премиум",3,2)),FALSE),0))</f>
         <v/>
       </c>
       <c r="T60" s="24" t="n"/>
@@ -3623,7 +3635,7 @@
         <v/>
       </c>
       <c r="Y60" s="21">
-        <f>IF($O60="","",ABS(Q60)+ABS(R60)+ABS(S60/(P60*(1+Q60)))+ABS(N(T60))+ABS(N(U60))+ABS(N(V60)))</f>
+        <f>IF($O60="","",ABS(Q60)+ABS(R60)+ABS(N(T60))+ABS(N(U60))+ABS(N(V60)))</f>
         <v/>
       </c>
       <c r="Z60" s="25">
@@ -3631,7 +3643,7 @@
         <v/>
       </c>
       <c r="AA60" s="25">
-        <f>IF($O60="","",IF(Z60="Да",IFERROR(VLOOKUP(B60,Параметры!$A$17:$B$19,2,FALSE),0.4)/(Y60+0.1),0))</f>
+        <f>IF($O60="","",IF(Z60="Да",IFERROR(VLOOKUP(B60,Параметры!$A$17:$B$19,2,FALSE),0.4)/(Y60+ABS(S60/(P60*(1+Q60)))+0.1),0))</f>
         <v/>
       </c>
       <c r="AB60" s="21">
@@ -3654,7 +3666,7 @@
     <mergeCell ref="E13:N13"/>
     <mergeCell ref="D4:G4"/>
   </mergeCells>
-  <dataValidations count="5">
+  <dataValidations count="6">
     <dataValidation sqref="B21:B60" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"1,2,3"</formula1>
     </dataValidation>
@@ -3662,10 +3674,13 @@
       <formula1>"Активно,Снято,Сделка"</formula1>
     </dataValidation>
     <dataValidation sqref="M21:M60" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>Параметры!$A$10:$A$14</formula1>
+      <formula1>Параметры!$A$10:$A$12</formula1>
     </dataValidation>
     <dataValidation sqref="B10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>Параметры!$A$10:$A$14</formula1>
+      <formula1>Параметры!$A$10:$A$12</formula1>
+    </dataValidation>
+    <dataValidation sqref="B14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Комфорт,Премиум"</formula1>
     </dataValidation>
     <dataValidation sqref="B7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Продажа,Аренда"</formula1>
@@ -3681,12 +3696,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="70" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3739,7 +3755,7 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>РЕМОНТ / СОСТОЯНИЕ — стоимость уровня отделки (от нуля)</t>
+          <t>РЕМОНТ — стоимость отделки от нуля, БЕЗ мебели (класс объекта — в блоке «Наш объект»)</t>
         </is>
       </c>
     </row>
@@ -3751,10 +3767,15 @@
       </c>
       <c r="B9" s="28" t="inlineStr">
         <is>
-          <t>Продажа, ₽ за м²</t>
+          <t>Комфорт, ₽ за м²</t>
         </is>
       </c>
       <c r="C9" s="28" t="inlineStr">
+        <is>
+          <t>Премиум, ₽ за м²</t>
+        </is>
+      </c>
+      <c r="D9" s="28" t="inlineStr">
         <is>
           <t>Аренда, ₽ за м² в месяц</t>
         </is>
@@ -3772,6 +3793,9 @@
       <c r="C10" s="12" t="n">
         <v>0</v>
       </c>
+      <c r="D10" s="12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -3783,46 +3807,33 @@
         <v>12000</v>
       </c>
       <c r="C11" s="12" t="n">
+        <v>12000</v>
+      </c>
+      <c r="D11" s="12" t="n">
         <v>50</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Стандартный ремонт</t>
+          <t>С ремонтом (без мебели)</t>
         </is>
       </c>
       <c r="B12" s="12" t="n">
-        <v>35000</v>
+        <v>100000</v>
       </c>
       <c r="C12" s="12" t="n">
+        <v>250000</v>
+      </c>
+      <c r="D12" s="12" t="n">
         <v>150</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Качественный / дизайнерский</t>
-        </is>
-      </c>
-      <c r="B13" s="12" t="n">
-        <v>70000</v>
-      </c>
-      <c r="C13" s="12" t="n">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Премиум + мебель и техника</t>
-        </is>
-      </c>
-      <c r="B14" s="12" t="n">
-        <v>120000</v>
-      </c>
-      <c r="C14" s="12" t="n">
-        <v>450</v>
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Мебель и техника в корректировку ремонта не входят — если у аналога есть мебель, это ручная корректировка «Прочее».</t>
+        </is>
       </c>
     </row>
     <row r="16">
@@ -3905,7 +3916,7 @@
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
         <is>
-          <t>2. Заполните блок «Наш объект» (площадь, сделка, ремонт — обязательно).</t>
+          <t>2. Заполните блок «Наш объект» (сделка, площадь, ремонт, класс — обязательно). Ремонт: комфорт — 100 000 ₽/м², премиум — 250 000 ₽/м², без мебели.</t>
         </is>
       </c>
     </row>
@@ -3940,7 +3951,7 @@
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>7. Аналог с общей корректировкой больше 30 % не учитывается автоматически.</t>
+          <t>7. Аналог с общей корректировкой больше 30 % (без учёта ремонта) не учитывается автоматически. Разница в ремонте снижает вес аналога.</t>
         </is>
       </c>
     </row>
